--- a/client/public/templates/PriceRight_Products_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Products_Import_Template.xlsx
@@ -398,14 +398,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A74"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Products + BOM Import Template</v>
+        <v>PriceRight — Products Import Template</v>
       </c>
     </row>
     <row r="2">
@@ -415,80 +415,386 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Fill in your data on the Import Data sheet.</v>
+        <v>HOW TO USE THIS TEMPLATE</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>One row per BOM line. Keep Product Name, Category, Production Mode, Batch Yield, Overhead %, Profit on Cost %, and SKU identical for every row of the same product.</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>STEPS:</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Product Name (required), Category, Production Mode (single or batch), Batch Yield, Overhead %, Profit on Cost %, SKU, Material Name (required), Quantity, Unit.</v>
+        <v>1. Click the "Import Data" tab at the bottom of this file</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>2. Review the sample rows to understand the expected format</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Production Mode: single = 1 unit per run | batch = Batch Yield units per run.</v>
+        <v>3. Delete the sample data rows (rows 2 and below)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Overhead %: overhead applied to material cost (e.g. 15 = 15%). Defaults to 0 if blank.</v>
+        <v xml:space="preserve">   — Keep row 1 (the column headers) — do not delete or edit it</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Profit on Cost %: profit margin on total cost, 0-99 (e.g. 25 = 25%). Required.</v>
+        <v>4. Enter your real data starting from row 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SKU: optional product code.</v>
+        <v>5. Save the file (keep the .xlsx format)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Unit column is informational only — the material unit is determined by the material record.</v>
+        <v>6. In PriceRight go to Products → More → Import and select this file</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Material Name must exactly match a raw material or intermediate already saved in PriceRight.</v>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>NOTE: Each product can have multiple BOM lines.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Add one row per material. Repeat the Product Name,</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SKU, Category and settings on each row for the same product.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Import all materials (primary and intermediate) before importing products.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>IMPORTANT NOTES:</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>— Do not rename or delete any column headers</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>— Do not add extra columns</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>— Leave optional fields blank if not needed</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>— Currency codes must match currencies set up in PriceRight</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>COLUMN GUIDE:</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">  Product Name — Required</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">    Full name of the finished product</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">    Example: Peanut Butter 250g</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">  SKU — Optional</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">    Product code or barcode reference</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">    Example: PB-250</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">  Category — Required</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">    Product category</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">    Example: Spreads</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">  Unit — Optional</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    Unit of sale</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">    Example: Ea  Kg  L</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">  Batch Size — Optional</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">    Number of units produced per production run</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Example: 500  (500 units per batch)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">  Overhead % — Optional (default: 0)</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">    Production overhead as a percentage</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">    Example: 20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">  Profit on Cost % — Optional</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Target profit margin on cost</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Example: 25  (means 25% profit on cost)</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">  Material Name — Required</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Name of a material used in the product BOM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Must already exist in PriceRight</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Example: Refined Peanut Paste</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">  Material Quantity — Required</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    Quantity of material per batch</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Example: 130  (130 Kg per batch of 500 units)</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">  Material Type — Optional</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    primary or intermediate</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve">    Example: intermediate</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">  Notes — Optional</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Additional notes</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Example: Main ingredient</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SAMPLE DATA:</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>The Import Data sheet contains sample rows showing the correct format.</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Delete them before importing.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A74"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K5"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,36 +802,179 @@
         <v>Product Name</v>
       </c>
       <c r="B1" t="str">
+        <v>SKU</v>
+      </c>
+      <c r="C1" t="str">
         <v>Category</v>
       </c>
-      <c r="C1" t="str">
-        <v>Production Mode</v>
-      </c>
       <c r="D1" t="str">
-        <v>Batch Yield</v>
+        <v>Unit</v>
       </c>
       <c r="E1" t="str">
+        <v>Batch Size</v>
+      </c>
+      <c r="F1" t="str">
         <v>Overhead %</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Profit on Cost %</v>
-      </c>
-      <c r="G1" t="str">
-        <v>SKU</v>
       </c>
       <c r="H1" t="str">
         <v>Material Name</v>
       </c>
       <c r="I1" t="str">
-        <v>Quantity</v>
+        <v>Material Quantity</v>
       </c>
       <c r="J1" t="str">
-        <v>Unit</v>
+        <v>Material Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Peanut Butter 250g</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PB-250</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Spreads</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Ea</v>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Refined Peanut Paste</v>
+      </c>
+      <c r="I2">
+        <v>130</v>
+      </c>
+      <c r="J2" t="str">
+        <v>intermediate</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Main ingredient</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Peanut Butter 250g</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PB-250</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Spreads</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Ea</v>
+      </c>
+      <c r="E3">
+        <v>500</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Packaging Film (Roll)</v>
+      </c>
+      <c r="I3">
+        <v>135</v>
+      </c>
+      <c r="J3" t="str">
+        <v>primary</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Packaging — 0.27m per unit</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Blended Spice Mix 100g</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BSM-100</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Seasonings</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Ea</v>
+      </c>
+      <c r="E4">
+        <v>800</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Blended Pepper Mix</v>
+      </c>
+      <c r="I4">
+        <v>20</v>
+      </c>
+      <c r="J4" t="str">
+        <v>intermediate</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Main spice blend</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Blended Spice Mix 100g</v>
+      </c>
+      <c r="B5" t="str">
+        <v>BSM-100</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Seasonings</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Ea</v>
+      </c>
+      <c r="E5">
+        <v>800</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Sachet Film 100g</v>
+      </c>
+      <c r="I5">
+        <v>800</v>
+      </c>
+      <c r="J5" t="str">
+        <v>primary</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Packaging sachet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/client/public/templates/PriceRight_Products_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Products_Import_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A70"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
@@ -740,49 +740,29 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">  Notes — Optional</v>
+        <v>SAMPLE DATA:</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Additional notes</v>
+        <v>The Import Data sheet contains sample rows showing the correct format.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Example: Main ingredient</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>SAMPLE DATA:</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>The Import Data sheet contains sample rows showing the correct format.</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
         <v>Delete them before importing.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -794,7 +774,6 @@
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="21.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,9 +807,6 @@
       <c r="J1" t="str">
         <v>Material Type</v>
       </c>
-      <c r="K1" t="str">
-        <v>Notes</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -863,9 +839,6 @@
       <c r="J2" t="str">
         <v>intermediate</v>
       </c>
-      <c r="K2" t="str">
-        <v>Main ingredient</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -898,9 +871,6 @@
       <c r="J3" t="str">
         <v>primary</v>
       </c>
-      <c r="K3" t="str">
-        <v>Packaging — 0.27m per unit</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -933,9 +903,6 @@
       <c r="J4" t="str">
         <v>intermediate</v>
       </c>
-      <c r="K4" t="str">
-        <v>Main spice blend</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -968,13 +935,10 @@
       <c r="J5" t="str">
         <v>primary</v>
       </c>
-      <c r="K5" t="str">
-        <v>Packaging sachet</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>